--- a/contents/member-info.xlsx
+++ b/contents/member-info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/Github/NTU-E3-Center.github.io/contents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39FC56E-CBE6-D34E-A05E-D5F8410AF0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79114A5-CC33-5441-972A-FC31918539D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="244">
   <si>
     <t>WebID</t>
   </si>
@@ -265,11 +264,6 @@
     <t>Harper completed her **B.S. in Civil Engineering** at National Central University (NCU), Taoyuan, in 2023, and pursued her graduate studies in the Computer-Aided Engineering (CAE) division of the Civil Engineering Department at National Taiwan University (NTU). In February 2025, she advanced directly into the **Ph.D. program** at NTU. Her research focuses on computer vision applications, with particular interests in medical imaging analysis and energy forecasting.</t>
   </si>
   <si>
-    <t>Ph.D. Student,
-Department of Civil Engineering,
-National Taiwan University</t>
-  </si>
-  <si>
     <t>/ Computer Vision 
 / Medical Image Analysis 
 / Energy Forecasting</t>
@@ -292,11 +286,6 @@
   <si>
     <t>Ray is a **Ph.D. student** at National Taiwan University, specializing in the intersection of **data analytics, artificial intelligence (AI), and Geographic Information Systems (GIS)**. His research is driven by a focus on green mobility, environmental policy, and energy economics, with a dedicated interest in leveraging data-driven decision-making to advance global net-zero goals and the development of sustainable smart cities.
 With a strong technical background in machine learning and spatial analysis, Ray focuses on modeling complex urban systems to inform more effective environmental strategies. He is committed to interdisciplinary collaboration and is actively involved in research initiatives that bridge the gap between advanced computational techniques and actionable policy frameworks.</t>
-  </si>
-  <si>
-    <t>Ph.D. Student,
-Department of Civil Engineering,
-National Taiwan University.</t>
   </si>
   <si>
     <t>/ Green Mobility &amp; Sustainable Transport 
@@ -350,11 +339,6 @@
     <t>Derek graduated from the **Department of Chemical Engineering** at National Taiwan University of Science and Technology in 2024. He is currently pursuing a **master’s degree** at the Graduate Institute of Chemical Engineering at National Taiwan University, under the guidance of Professor Lisa Hsieh. His current research focuses on **sustainable supply chains**, including topics such as **Green Vehicle Routing Problems (Green VRP)**, joint distribution, and hub-and-spoke network design.</t>
   </si>
   <si>
-    <t>Master's Student,
-Department of Chemical Engineering,
-National Taiwan University</t>
-  </si>
-  <si>
     <t>/ Sustainable Supply Chain Management 
 / Green Vehicle Routing Problems (Green VRP) 
 / Joint Distribution Systems 
@@ -394,11 +378,6 @@
     <t>Leo, also known by the nickname **DuoDuo(多多)**, completed his **undergraduate degree in Civil Engineering** at National Taiwan University (NTU) in 2025. He is currently a member of the **Computer-Aided Engineering (CAE)** division of NTU’s Civil Engineering department. His interests include playing volleyball, board games, and exploring new experiences. His research focuses on integrating **large language models (LLMs)** with **computer vision** to control autonomous vehicles, aiming to ensure safe driving, provide transparent explanations of model decisions, and optimize energy efficiency.</t>
   </si>
   <si>
-    <t>Master's Student,
-Department of Civil Engineering,
-National Taiwan University</t>
-  </si>
-  <si>
     <t>/ Autonomous Vehicles 
 / Computer Vision</t>
   </si>
@@ -481,10 +460,6 @@
   </si>
   <si>
     <t>Yi-Fang is a **graduate student** in the **Master’s Program in Disaster Risk Reduction and Resilience** at National Taiwan University, with a background in **civil engineering** and professional experience in large-scale energy infrastructure projects. Her research focuses on **energy planning**, with particular interest in integrating climate change risk assessment, resilience strategies, and sustainable energy systems. Prior to her graduate studies, she worked as a **civil engineer** and **project coordination specialist** on offshore substation construction projects, and later as a **research assistant** on climate change adaptation planning for Taiwan’s national parks. She is especially interested in bridging the fields of infrastructure development, climate resilience, and renewable energy to support sustainable transitions in both urban and natural environments.</t>
-  </si>
-  <si>
-    <t>Master’s Program in Disaster Risk Reduction and Resilience,
-National Taiwan University</t>
   </si>
   <si>
     <t>/ Sustainable Energy Planning</t>
@@ -735,76 +710,115 @@
     <t>Yu Fang Shen</t>
   </si>
   <si>
-    <t>CHIH-YA CHENG</t>
-  </si>
-  <si>
     <t>Chun-Hao Huang</t>
   </si>
   <si>
-    <t>HIGASHI MASAKI</t>
-  </si>
-  <si>
     <t>Yugo</t>
   </si>
   <si>
     <t>Masaki</t>
   </si>
   <si>
-    <t>Master's Student,
+    <t>Undergraduate (Pre-Master's) Student</t>
+  </si>
+  <si>
+    <t>An-Ching Chung</t>
+  </si>
+  <si>
+    <t>Yi-Ya Yu</t>
+  </si>
+  <si>
+    <t>Hsun-Yen Wu</t>
+  </si>
+  <si>
+    <t>Shao Yang Cheung</t>
+  </si>
+  <si>
+    <t>Yu-Ting Huang</t>
+  </si>
+  <si>
+    <t>Yu-Shin Hu</t>
+  </si>
+  <si>
+    <t>Pei-Ci Chen</t>
+  </si>
+  <si>
+    <t>Kai-Yun Lo</t>
+  </si>
+  <si>
+    <t>Yi-Fan Feng</t>
+  </si>
+  <si>
+    <t>Jing-Siou Tseng</t>
+  </si>
+  <si>
+    <t>Yuan-Shin Fu</t>
+  </si>
+  <si>
+    <t>Chia-Yu Tsai</t>
+  </si>
+  <si>
+    <t>Tsung-Heng Chang</t>
+  </si>
+  <si>
+    <t>Wei-Hsuan Chen</t>
+  </si>
+  <si>
+    <t>Yu-Jui Chang</t>
+  </si>
+  <si>
+    <t>Cheng-Ye Li</t>
+  </si>
+  <si>
+    <t>Chih-Ya Cheng</t>
+  </si>
+  <si>
+    <t>Higashi Masaki</t>
+  </si>
+  <si>
+    <t>Year 2 Ph.D. Student,
+Department of Civil Engineering,
+National Taiwan University</t>
+  </si>
+  <si>
+    <t>Year 1 Ph.D. Student,
+Department of Civil Engineering,
+National Taiwan University.</t>
+  </si>
+  <si>
+    <t>Year 1 Master's Student,
 Department of Civil Engineering,
 National Taiwan University
 (Double Degree from Kyushu University)</t>
   </si>
   <si>
-    <t>Undergraduate (Pre-Master's) Student</t>
-  </si>
-  <si>
-    <t>An-Ching Chung</t>
-  </si>
-  <si>
-    <t>Yi-Ya Yu</t>
-  </si>
-  <si>
-    <t>Hsun-Yen Wu</t>
-  </si>
-  <si>
-    <t>Shao Yang Cheung</t>
-  </si>
-  <si>
-    <t>Yu-Ting Huang</t>
-  </si>
-  <si>
-    <t>Yu-Shin Hu</t>
-  </si>
-  <si>
-    <t>Pei-Ci Chen</t>
-  </si>
-  <si>
-    <t>Kai-Yun Lo</t>
-  </si>
-  <si>
-    <t>Yi-Fan Feng</t>
-  </si>
-  <si>
-    <t>Jing-Siou Tseng</t>
-  </si>
-  <si>
-    <t>Yuan-Shin Fu</t>
-  </si>
-  <si>
-    <t>Chia-Yu Tsai</t>
-  </si>
-  <si>
-    <t>Tsung-Heng Chang</t>
-  </si>
-  <si>
-    <t>Wei-Hsuan Chen</t>
-  </si>
-  <si>
-    <t>Yu-Jui Chang</t>
-  </si>
-  <si>
-    <t>Cheng-Ye Li</t>
+    <t>Year 3 Master's Student (Part-time),
+Department of Civil Engineering,
+National Taiwan University</t>
+  </si>
+  <si>
+    <t>Year 2 Master's Student,
+Department of Civil Engineering,
+National Taiwan University</t>
+  </si>
+  <si>
+    <t>Year 2 Master's Student,
+Department of Chemical Engineering,
+National Taiwan University</t>
+  </si>
+  <si>
+    <t>Year 1 Master’s Program in Disaster Risk Reduction and Resilience,
+National Taiwan University</t>
+  </si>
+  <si>
+    <t>Year 1 Master's Student,
+Department of Civil Engineering,
+National Taiwan University</t>
+  </si>
+  <si>
+    <t>Year 1 Master's Student,
+Department of Chemical Engineering,
+National Taiwan University</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
@@ -1264,7 +1278,7 @@
         <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H2" s="1" t="str">
         <f t="shared" ref="H2:H38" si="0">LOWER(SUBSTITUTE(SUBSTITUTE(TRIM(G2),"-","")," ",""))</f>
@@ -1319,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1374,7 +1388,7 @@
         <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1476,13 +1490,13 @@
         <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1529,7 +1543,7 @@
         <v>59</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1551,11 +1565,11 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1" t="s">
-        <v>69</v>
+        <v>235</v>
       </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -1602,10 +1616,10 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>68</v>
@@ -1616,32 +1630,32 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>hungjuilin</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>60</v>
@@ -1655,13 +1669,13 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1" t="s">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="112" x14ac:dyDescent="0.2">
@@ -1669,22 +1683,22 @@
         <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="H10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1692,13 +1706,13 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>67</v>
@@ -1706,7 +1720,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1716,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>36</v>
@@ -1725,13 +1739,13 @@
         <v>57</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H11" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1739,10 +1753,10 @@
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>61</v>
@@ -1753,7 +1767,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1" t="s">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1763,22 +1777,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="H12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1786,10 +1800,10 @@
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>61</v>
@@ -1800,7 +1814,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1" t="s">
-        <v>107</v>
+        <v>239</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1810,22 +1824,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="H13" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1833,10 +1847,10 @@
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>61</v>
@@ -1847,7 +1861,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1" t="s">
-        <v>107</v>
+        <v>239</v>
       </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -1857,35 +1871,35 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="H14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>enyichou</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>61</v>
@@ -1896,13 +1910,13 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1" t="s">
-        <v>94</v>
+        <v>240</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="64" x14ac:dyDescent="0.2">
@@ -1910,38 +1924,38 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yifangchang</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>67</v>
@@ -1949,13 +1963,13 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -1963,38 +1977,38 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>shuochenli</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>shuochenli</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>67</v>
@@ -2002,13 +2016,13 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1" t="s">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -2016,38 +2030,38 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yurankeng</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>67</v>
@@ -2055,13 +2069,13 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1" t="s">
-        <v>94</v>
+        <v>243</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -2069,22 +2083,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="H18" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2092,13 +2106,13 @@
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>67</v>
@@ -2106,7 +2120,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1" t="s">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -2116,38 +2130,38 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>houchuanchen</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>67</v>
@@ -2155,13 +2169,13 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1" t="s">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -2169,22 +2183,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="H20" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2192,13 +2206,13 @@
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>67</v>
@@ -2206,7 +2220,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1" t="s">
-        <v>94</v>
+        <v>243</v>
       </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -2216,22 +2230,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2239,13 +2253,13 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>67</v>
@@ -2253,7 +2267,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -2263,22 +2277,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H22" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2286,13 +2300,13 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>67</v>
@@ -2300,7 +2314,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -2310,22 +2324,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H23" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2333,13 +2347,13 @@
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>67</v>
@@ -2347,7 +2361,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2357,22 +2371,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="H24" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2380,13 +2394,13 @@
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>67</v>
@@ -2394,7 +2408,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2404,35 +2418,35 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>chunhaohuang</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>67</v>
@@ -2440,7 +2454,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -2450,32 +2464,32 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yugoimoto</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>52</v>
@@ -2496,35 +2510,35 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="H27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>chiayutsai</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="L27" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>31</v>
@@ -2540,35 +2554,35 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="H28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tsunghengchang</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>31</v>
@@ -2584,7 +2598,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>24</v>
@@ -2593,23 +2607,23 @@
         <v>57</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="H29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>kaiyunlo</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>30</v>
@@ -2628,32 +2642,32 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>weihsuanchen</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>30</v>
@@ -2672,7 +2686,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>24</v>
@@ -2681,23 +2695,23 @@
         <v>57</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yifanfeng</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>30</v>
@@ -2716,22 +2730,22 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="H32" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2739,10 +2753,10 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>39</v>
@@ -2761,7 +2775,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>36</v>
@@ -2770,13 +2784,13 @@
         <v>57</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H33" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2784,10 +2798,10 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>39</v>
@@ -2806,7 +2820,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>36</v>
@@ -2815,26 +2829,26 @@
         <v>57</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yuanhsichien</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>39</v>
@@ -2845,11 +2859,11 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -2857,22 +2871,22 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="H35" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2880,10 +2894,10 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>52</v>
@@ -2902,22 +2916,22 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H36" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2925,10 +2939,10 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>52</v>
@@ -2947,7 +2961,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>48</v>
@@ -2956,13 +2970,13 @@
         <v>57</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="H37" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2970,10 +2984,10 @@
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>52</v>
@@ -2992,7 +3006,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>48</v>
@@ -3001,13 +3015,13 @@
         <v>57</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="H38" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3015,10 +3029,10 @@
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>52</v>

--- a/contents/member-info.xlsx
+++ b/contents/member-info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/Github/NTU-E3-Center.github.io/contents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79114A5-CC33-5441-972A-FC31918539D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCAA57C-0A87-2B46-90C0-BD26930F8B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -375,9 +375,6 @@
     <t>'25</t>
   </si>
   <si>
-    <t>Leo, also known by the nickname **DuoDuo(多多)**, completed his **undergraduate degree in Civil Engineering** at National Taiwan University (NTU) in 2025. He is currently a member of the **Computer-Aided Engineering (CAE)** division of NTU’s Civil Engineering department. His interests include playing volleyball, board games, and exploring new experiences. His research focuses on integrating **large language models (LLMs)** with **computer vision** to control autonomous vehicles, aiming to ensure safe driving, provide transparent explanations of model decisions, and optimize energy efficiency.</t>
-  </si>
-  <si>
     <t>/ Autonomous Vehicles 
 / Computer Vision</t>
   </si>
@@ -819,6 +816,9 @@
     <t>Year 1 Master's Student,
 Department of Chemical Engineering,
 National Taiwan University</t>
+  </si>
+  <si>
+    <t>Leo, also known by the nickname **DuoDuo** (多多), completed his **undergraduate degree in Civil Engineering** at National Taiwan University (NTU) in 2025. He is currently a member of the **Computer-Aided Engineering (CAE)** division of NTU’s Civil Engineering department. His interests include playing volleyball, board games, and exploring new experiences. His research focuses on integrating **large language models (LLMs)** with **computer vision** to control autonomous vehicles, aiming to ensure safe driving, provide transparent explanations of model decisions, and optimize energy efficiency.</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
@@ -1278,7 +1278,7 @@
         <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H2" s="1" t="str">
         <f t="shared" ref="H2:H38" si="0">LOWER(SUBSTITUTE(SUBSTITUTE(TRIM(G2),"-","")," ",""))</f>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1388,7 +1388,7 @@
         <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1490,13 +1490,13 @@
         <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1543,7 +1543,7 @@
         <v>59</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1565,11 +1565,11 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -1616,7 +1616,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>69</v>
@@ -1645,7 +1645,7 @@
         <v>74</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1669,7 +1669,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>76</v>
@@ -1683,7 +1683,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>79</v>
@@ -1692,13 +1692,13 @@
         <v>57</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>82</v>
@@ -1720,7 +1720,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1745,7 +1745,7 @@
         <v>95</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H11" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1767,7 +1767,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1792,7 +1792,7 @@
         <v>85</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1814,7 +1814,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1839,7 +1839,7 @@
         <v>81</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H13" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1861,7 +1861,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -1910,7 +1910,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>92</v>
@@ -1933,23 +1933,23 @@
         <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="H15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yifangchang</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>82</v>
@@ -1963,13 +1963,13 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -2016,13 +2016,13 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>103</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -2039,23 +2039,23 @@
         <v>87</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="H17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yurankeng</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>82</v>
@@ -2069,13 +2069,13 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -2092,13 +2092,13 @@
         <v>57</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H18" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>82</v>
@@ -2120,7 +2120,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -2139,23 +2139,23 @@
         <v>57</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>houchuanchen</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>82</v>
@@ -2169,13 +2169,13 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="80" x14ac:dyDescent="0.2">
@@ -2192,13 +2192,13 @@
         <v>87</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H20" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>82</v>
@@ -2220,7 +2220,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -2230,22 +2230,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2253,13 +2253,13 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>67</v>
@@ -2267,7 +2267,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -2277,22 +2277,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H22" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2300,13 +2300,13 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>67</v>
@@ -2314,7 +2314,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -2324,22 +2324,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="G23" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H23" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2347,13 +2347,13 @@
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>67</v>
@@ -2361,7 +2361,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2371,22 +2371,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H24" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2394,13 +2394,13 @@
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>67</v>
@@ -2408,7 +2408,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2418,35 +2418,35 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>chunhaohuang</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>67</v>
@@ -2454,7 +2454,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -2464,32 +2464,32 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yugoimoto</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>52</v>
@@ -2510,35 +2510,35 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>chiayutsai</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="H27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>chiayutsai</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>31</v>
@@ -2554,35 +2554,35 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>tsunghengchang</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>tsunghengchang</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>31</v>
@@ -2598,7 +2598,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>24</v>
@@ -2607,23 +2607,23 @@
         <v>57</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>kaiyunlo</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>30</v>
@@ -2642,7 +2642,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>24</v>
@@ -2654,20 +2654,20 @@
         <v>37</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>weihsuanchen</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>30</v>
@@ -2686,7 +2686,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>24</v>
@@ -2695,23 +2695,23 @@
         <v>57</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yifanfeng</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>30</v>
@@ -2730,7 +2730,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>36</v>
@@ -2739,13 +2739,13 @@
         <v>87</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H32" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2753,10 +2753,10 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>39</v>
@@ -2775,7 +2775,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>36</v>
@@ -2784,13 +2784,13 @@
         <v>57</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="G33" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H33" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2798,10 +2798,10 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>39</v>
@@ -2820,7 +2820,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>36</v>
@@ -2829,26 +2829,26 @@
         <v>57</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>yuanhsichien</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>yuanhsichien</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="J34" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>39</v>
@@ -2859,11 +2859,11 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -2871,7 +2871,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>48</v>
@@ -2880,13 +2880,13 @@
         <v>87</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H35" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2894,10 +2894,10 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>52</v>
@@ -2916,7 +2916,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>48</v>
@@ -2925,13 +2925,13 @@
         <v>87</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="G36" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H36" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2939,10 +2939,10 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>52</v>
@@ -2961,7 +2961,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>48</v>
@@ -2970,13 +2970,13 @@
         <v>57</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H37" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2984,10 +2984,10 @@
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>52</v>
@@ -3006,7 +3006,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>48</v>
@@ -3015,13 +3015,13 @@
         <v>57</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H38" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3029,10 +3029,10 @@
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>52</v>

--- a/contents/member-info.xlsx
+++ b/contents/member-info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/Github/NTU-E3-Center.github.io/contents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCAA57C-0A87-2B46-90C0-BD26930F8B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D02D851-FDCC-804D-AE7D-C59032AD2142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="246">
   <si>
     <t>WebID</t>
   </si>
@@ -819,6 +819,15 @@
   </si>
   <si>
     <t>Leo, also known by the nickname **DuoDuo** (多多), completed his **undergraduate degree in Civil Engineering** at National Taiwan University (NTU) in 2025. He is currently a member of the **Computer-Aided Engineering (CAE)** division of NTU’s Civil Engineering department. His interests include playing volleyball, board games, and exploring new experiences. His research focuses on integrating **large language models (LLMs)** with **computer vision** to control autonomous vehicles, aiming to ensure safe driving, provide transparent explanations of model decisions, and optimize energy efficiency.</t>
+  </si>
+  <si>
+    <t>/Energy System Optimization
+/Vehicle-to-Building (V2B) Strategy</t>
+  </si>
+  <si>
+    <t>/Smart Grid Modeling
+/Energy Management Systems
+/Low Carbon Logistics</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1482,9 @@
       <c r="P5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>53</v>
       </c>
@@ -1518,7 +1529,9 @@
       <c r="P6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>245</v>
+      </c>
       <c r="R6" s="1" t="s">
         <v>20</v>
       </c>

--- a/contents/member-info.xlsx
+++ b/contents/member-info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/Github/NTU-E3-Center.github.io/contents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/NTU-E3-Center.github.io/contents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D02D851-FDCC-804D-AE7D-C59032AD2142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32519EFD-E392-D441-B682-16A23BC3E5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="265">
   <si>
     <t>WebID</t>
   </si>
@@ -829,12 +829,69 @@
 /Energy Management Systems
 /Low Carbon Logistics</t>
   </si>
+  <si>
+    <t>metaDescription</t>
+  </si>
+  <si>
+    <t>Dr. I-Yun Lisa Hsieh (謝依芸), Associate Professor at NTU &amp; Director of E3 Center. MIT PhD researching sustainable energy, electric mobility, and net-zero.</t>
+  </si>
+  <si>
+    <t>Google Scholar</t>
+  </si>
+  <si>
+    <t>ORCID</t>
+  </si>
+  <si>
+    <t>ResearchGate</t>
+  </si>
+  <si>
+    <t>NTU Scholars</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>0000-0002-1668-4094</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com.tw/citations?user=tUbPb-QAAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/profile/I-Yun-Lisa-Hsieh</t>
+  </si>
+  <si>
+    <t>https://scholars.lib.ntu.edu.tw/entities/person/db907a6f-b506-436e-be36-9acb69ca26d4/indicators</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/i-yun-lisa-hsieh/</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/lisahsieh0410</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/sean.shei/</t>
+  </si>
+  <si>
+    <t>www.linkedin.com/in/sean-shei-61409b293</t>
+  </si>
+  <si>
+    <t>0009-0001-5290-5544</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/profile/Cheng-Hsiang-Shei</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=qG7wiMEAAAAJ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -844,6 +901,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -866,19 +931,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -1187,31 +1254,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="10" width="30" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="38.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.33203125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="187" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="3.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="38.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="151.5" style="1" customWidth="1"/>
+    <col min="19" max="19" width="32.6640625" style="1" customWidth="1"/>
+    <col min="20" max="24" width="19.1640625" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1266,8 +1335,29 @@
       <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="160" x14ac:dyDescent="0.2">
+      <c r="S1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="208" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1317,12 +1407,11 @@
       <c r="P2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" s="1"/>
       <c r="R2" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="176" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="192" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1372,12 +1461,11 @@
       <c r="P3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="1"/>
       <c r="R3" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="240" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="288" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1427,12 +1515,26 @@
       <c r="P4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="112" x14ac:dyDescent="0.2">
+      <c r="T4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="144" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1489,14 +1591,13 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="272" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="304" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1522,10 +1623,6 @@
       <c r="K6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
       <c r="P6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1535,8 +1632,29 @@
       <c r="R6" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="80" x14ac:dyDescent="0.2">
+      <c r="S6" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1562,7 +1680,6 @@
         <f t="shared" si="0"/>
         <v>junweiding</v>
       </c>
-      <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
         <v>54</v>
       </c>
@@ -1575,17 +1692,14 @@
       <c r="M7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
       <c r="P7" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="Q7" s="1"/>
       <c r="R7" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="80" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1626,8 +1740,6 @@
       <c r="M8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
       <c r="P8" s="1" t="s">
         <v>234</v>
       </c>
@@ -1638,7 +1750,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="112" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="112" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1679,8 +1791,6 @@
       <c r="M9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
       <c r="P9" s="1" t="s">
         <v>235</v>
       </c>
@@ -1691,7 +1801,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="112" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="112" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>36</v>
       </c>
@@ -1710,14 +1820,13 @@
       <c r="F10" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>233</v>
       </c>
       <c r="H10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>higashimasaki</v>
       </c>
-      <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
         <v>112</v>
       </c>
@@ -1730,15 +1839,11 @@
       <c r="M10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-    </row>
-    <row r="11" spans="1:18" ht="80" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1764,7 +1869,6 @@
         <f t="shared" si="0"/>
         <v>anchingchung</v>
       </c>
-      <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
         <v>93</v>
       </c>
@@ -1777,15 +1881,11 @@
       <c r="M11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
       <c r="P11" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-    </row>
-    <row r="12" spans="1:18" ht="80" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1811,7 +1911,6 @@
         <f t="shared" si="0"/>
         <v>yiyayu</v>
       </c>
-      <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
         <v>83</v>
       </c>
@@ -1824,15 +1923,11 @@
       <c r="M12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
       <c r="P12" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-    </row>
-    <row r="13" spans="1:18" ht="80" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1858,7 +1953,6 @@
         <f t="shared" si="0"/>
         <v>hsunyenwu</v>
       </c>
-      <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
         <v>77</v>
       </c>
@@ -1871,15 +1965,11 @@
       <c r="M13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
       <c r="P13" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-    </row>
-    <row r="14" spans="1:18" ht="112" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:25" ht="112" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1920,8 +2010,6 @@
       <c r="M14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
       <c r="P14" s="1" t="s">
         <v>239</v>
       </c>
@@ -1932,7 +2020,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="64" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1973,8 +2061,6 @@
       <c r="M15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
       <c r="P15" s="1" t="s">
         <v>240</v>
       </c>
@@ -1985,7 +2071,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="80" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2026,8 +2112,6 @@
       <c r="M16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
       <c r="P16" s="1" t="s">
         <v>241</v>
       </c>
@@ -2079,8 +2163,6 @@
       <c r="M17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
       <c r="P17" s="1" t="s">
         <v>242</v>
       </c>
@@ -2117,7 +2199,6 @@
         <f t="shared" si="0"/>
         <v>shaoyangcheung</v>
       </c>
-      <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
         <v>109</v>
       </c>
@@ -2130,13 +2211,9 @@
       <c r="M18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
       <c r="P18" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
     </row>
     <row r="19" spans="1:18" ht="80" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
@@ -2179,8 +2256,6 @@
       <c r="M19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
       <c r="P19" s="1" t="s">
         <v>241</v>
       </c>
@@ -2217,7 +2292,6 @@
         <f t="shared" si="0"/>
         <v>yutinghuang</v>
       </c>
-      <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
         <v>122</v>
       </c>
@@ -2230,13 +2304,9 @@
       <c r="M20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
       <c r="P20" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
     </row>
     <row r="21" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -2257,14 +2327,13 @@
       <c r="F21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>209</v>
       </c>
       <c r="H21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>peitiyu</v>
       </c>
-      <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
         <v>131</v>
       </c>
@@ -2277,13 +2346,9 @@
       <c r="M21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
       <c r="P21" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
     </row>
     <row r="22" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
@@ -2304,14 +2369,13 @@
       <c r="F22" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>210</v>
       </c>
       <c r="H22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tingyelin</v>
       </c>
-      <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
         <v>137</v>
       </c>
@@ -2324,13 +2388,9 @@
       <c r="M22" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
       <c r="P22" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
@@ -2351,14 +2411,13 @@
       <c r="F23" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>211</v>
       </c>
       <c r="H23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>yufangshen</v>
       </c>
-      <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
         <v>142</v>
       </c>
@@ -2371,13 +2430,9 @@
       <c r="M23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
       <c r="P23" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
     </row>
     <row r="24" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
@@ -2398,14 +2453,13 @@
       <c r="F24" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>232</v>
       </c>
       <c r="H24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>chihyacheng</v>
       </c>
-      <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
         <v>146</v>
       </c>
@@ -2418,13 +2472,9 @@
       <c r="M24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
       <c r="P24" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
     </row>
     <row r="25" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
@@ -2445,7 +2495,7 @@
       <c r="F25" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>212</v>
       </c>
       <c r="H25" s="1" t="str">
@@ -2464,13 +2514,9 @@
       <c r="M25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
       <c r="P25" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
     </row>
     <row r="26" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -2491,7 +2537,7 @@
       <c r="F26" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="1" t="s">
         <v>191</v>
       </c>
       <c r="H26" s="1" t="str">
@@ -2510,13 +2556,9 @@
       <c r="M26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
       <c r="P26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
     </row>
     <row r="27" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
@@ -2556,11 +2598,6 @@
       <c r="M27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
     </row>
     <row r="28" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -2600,11 +2637,6 @@
       <c r="M28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
     </row>
     <row r="29" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
@@ -2644,11 +2676,6 @@
       <c r="M29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
     </row>
     <row r="30" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
@@ -2688,11 +2715,6 @@
       <c r="M30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
     </row>
     <row r="31" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
@@ -2732,11 +2754,6 @@
       <c r="M31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
     </row>
     <row r="32" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
@@ -2764,7 +2781,6 @@
         <f t="shared" si="0"/>
         <v>yuanshinfu</v>
       </c>
-      <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
         <v>182</v>
       </c>
@@ -2777,11 +2793,6 @@
       <c r="M32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
     </row>
     <row r="33" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
@@ -2809,7 +2820,6 @@
         <f t="shared" si="0"/>
         <v>jingsioutseng</v>
       </c>
-      <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
         <v>179</v>
       </c>
@@ -2822,11 +2832,6 @@
       <c r="M33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
     </row>
     <row r="34" spans="1:18" ht="80" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
@@ -2869,12 +2874,9 @@
       <c r="M34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="Q34" s="1"/>
       <c r="R34" s="1" t="s">
         <v>177</v>
       </c>
@@ -2905,7 +2907,6 @@
         <f t="shared" si="0"/>
         <v>yujuichang</v>
       </c>
-      <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
         <v>188</v>
       </c>
@@ -2918,11 +2919,6 @@
       <c r="M35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
     </row>
     <row r="36" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
@@ -2950,7 +2946,6 @@
         <f t="shared" si="0"/>
         <v>chengyeli</v>
       </c>
-      <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
         <v>185</v>
       </c>
@@ -2963,11 +2958,6 @@
       <c r="M36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
     </row>
     <row r="37" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
@@ -2995,7 +2985,6 @@
         <f t="shared" si="0"/>
         <v>yushinhu</v>
       </c>
-      <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
         <v>193</v>
       </c>
@@ -3008,11 +2997,6 @@
       <c r="M37" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
     </row>
     <row r="38" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
@@ -3040,7 +3024,6 @@
         <f t="shared" si="0"/>
         <v>peicichen</v>
       </c>
-      <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
         <v>196</v>
       </c>
@@ -3053,11 +3036,6 @@
       <c r="M38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V42" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -3071,6 +3049,18 @@
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="T6" r:id="rId1" xr:uid="{24A41E33-C86B-1744-BC76-7C365EBDABEB}"/>
+    <hyperlink ref="V6" r:id="rId2" xr:uid="{3F9F9868-CCC4-0E4C-A9B2-ABC7AFAFC108}"/>
+    <hyperlink ref="X6" r:id="rId3" xr:uid="{B64E472A-E346-C44F-9955-5F2012E1723F}"/>
+    <hyperlink ref="W6" r:id="rId4" xr:uid="{D4854485-627C-724D-966A-7E5E71442C20}"/>
+    <hyperlink ref="Y6" r:id="rId5" xr:uid="{BC9446D3-4A6B-D74F-BBA6-5DFD40321617}"/>
+    <hyperlink ref="Y4" r:id="rId6" xr:uid="{4C866E4E-CAF9-1040-95E4-4C9C2454535B}"/>
+    <hyperlink ref="W4" r:id="rId7" xr:uid="{410C066E-FF05-C942-A96A-A83F5FBDEF4A}"/>
+    <hyperlink ref="U4" r:id="rId8" display="https://orcid.org/0009-0001-5290-5544" xr:uid="{A5D22604-2496-BE4F-B9DD-562C5B47E295}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{D172C527-C1C4-C047-A757-BC75CC7426F9}"/>
+    <hyperlink ref="T4" r:id="rId10" xr:uid="{6F8425CF-B855-5A4A-B2B6-34D12B80B2AB}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contents/member-info.xlsx
+++ b/contents/member-info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/NTU-E3-Center.github.io/contents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32519EFD-E392-D441-B682-16A23BC3E5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02C2C1C-E0DF-DE42-96E9-DC2C07AA2991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="266">
   <si>
     <t>WebID</t>
   </si>
@@ -875,9 +875,6 @@
     <t>https://www.facebook.com/sean.shei/</t>
   </si>
   <si>
-    <t>www.linkedin.com/in/sean-shei-61409b293</t>
-  </si>
-  <si>
     <t>0009-0001-5290-5544</t>
   </si>
   <si>
@@ -885,6 +882,14 @@
   </si>
   <si>
     <t>https://scholar.google.com/citations?user=qG7wiMEAAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sean-shei-61409b293/</t>
+  </si>
+  <si>
+    <t>/Distributional Impacts of Climate and Energy Policy
+/Climate Policy and Global Inequality
+/Energy Transition and Electricity Market Reform</t>
   </si>
 </sst>
 </file>
@@ -1515,20 +1520,23 @@
       <c r="P4" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="Q4" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="R4" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T4" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="W4" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>260</v>

--- a/contents/member-info.xlsx
+++ b/contents/member-info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/NTU-E3-Center.github.io/contents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02C2C1C-E0DF-DE42-96E9-DC2C07AA2991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6195BE-FE7B-FF47-888D-C4DC48EDC4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="272">
   <si>
     <t>WebID</t>
   </si>
@@ -890,6 +890,24 @@
     <t>/Distributional Impacts of Climate and Energy Policy
 /Climate Policy and Global Inequality
 /Energy Transition and Electricity Market Reform</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=Djvdd44AAAAJ</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=JfG80RsAAAAJ</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=-hlSIJgAAAAJ</t>
+  </si>
+  <si>
+    <t>0009-0001-4608-919X</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/profile/Jian-Hern-Yeoh</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jianhern/</t>
   </si>
 </sst>
 </file>
@@ -1598,6 +1616,18 @@
       <c r="R5" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="T5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="6" spans="1:25" ht="304" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -1706,6 +1736,9 @@
       <c r="R7" s="1" t="s">
         <v>206</v>
       </c>
+      <c r="T7" s="2" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="8" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -1807,6 +1840,9 @@
       </c>
       <c r="R9" s="1" t="s">
         <v>75</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="112" x14ac:dyDescent="0.2">
@@ -3068,6 +3104,11 @@
     <hyperlink ref="U4" r:id="rId8" display="https://orcid.org/0009-0001-5290-5544" xr:uid="{A5D22604-2496-BE4F-B9DD-562C5B47E295}"/>
     <hyperlink ref="V4" r:id="rId9" xr:uid="{D172C527-C1C4-C047-A757-BC75CC7426F9}"/>
     <hyperlink ref="T4" r:id="rId10" xr:uid="{6F8425CF-B855-5A4A-B2B6-34D12B80B2AB}"/>
+    <hyperlink ref="T5" r:id="rId11" xr:uid="{4B38D0AD-2FC7-464D-9060-0D0FBCDDA9CB}"/>
+    <hyperlink ref="T7" r:id="rId12" xr:uid="{C7B4F0EB-6958-F54A-AF58-5BDA16E41654}"/>
+    <hyperlink ref="T9" r:id="rId13" xr:uid="{E2673CF1-94A5-2249-916F-2DCC53FC5CC1}"/>
+    <hyperlink ref="V5" r:id="rId14" xr:uid="{5AE67EF2-5E71-864C-90FE-CC4C98072E15}"/>
+    <hyperlink ref="W5" r:id="rId15" xr:uid="{C859D6CF-4C2E-2746-B2B4-BC6D99CC40FD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/contents/member-info.xlsx
+++ b/contents/member-info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianhern/Desktop/NTU-E3-Center.github.io/contents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6195BE-FE7B-FF47-888D-C4DC48EDC4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F13AB17-C57F-AC4B-9DE9-752D308D6F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="600" windowWidth="44200" windowHeight="26380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -869,9 +869,6 @@
     <t>Facebook</t>
   </si>
   <si>
-    <t>https://www.facebook.com/lisahsieh0410</t>
-  </si>
-  <si>
     <t>https://www.facebook.com/sean.shei/</t>
   </si>
   <si>
@@ -908,6 +905,9 @@
   </si>
   <si>
     <t>https://www.linkedin.com/in/jianhern/</t>
+  </si>
+  <si>
+    <t>0009-0005-5799-7280</t>
   </si>
 </sst>
 </file>
@@ -1514,10 +1514,10 @@
         <f t="shared" si="0"/>
         <v>chenghsiangshei</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -1539,25 +1539,25 @@
         <v>41</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T4" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="W4" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="U4" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="Y4" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="144" x14ac:dyDescent="0.2">
@@ -1617,16 +1617,16 @@
         <v>53</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="U5" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="304" x14ac:dyDescent="0.2">
@@ -1688,9 +1688,7 @@
       <c r="X6" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>259</v>
-      </c>
+      <c r="Y6" s="2"/>
     </row>
     <row r="7" spans="1:25" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -1737,7 +1735,7 @@
         <v>206</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="80" x14ac:dyDescent="0.2">
@@ -1842,7 +1840,10 @@
         <v>75</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="112" x14ac:dyDescent="0.2">
@@ -3098,17 +3099,18 @@
     <hyperlink ref="V6" r:id="rId2" xr:uid="{3F9F9868-CCC4-0E4C-A9B2-ABC7AFAFC108}"/>
     <hyperlink ref="X6" r:id="rId3" xr:uid="{B64E472A-E346-C44F-9955-5F2012E1723F}"/>
     <hyperlink ref="W6" r:id="rId4" xr:uid="{D4854485-627C-724D-966A-7E5E71442C20}"/>
-    <hyperlink ref="Y6" r:id="rId5" xr:uid="{BC9446D3-4A6B-D74F-BBA6-5DFD40321617}"/>
-    <hyperlink ref="Y4" r:id="rId6" xr:uid="{4C866E4E-CAF9-1040-95E4-4C9C2454535B}"/>
-    <hyperlink ref="W4" r:id="rId7" xr:uid="{410C066E-FF05-C942-A96A-A83F5FBDEF4A}"/>
-    <hyperlink ref="U4" r:id="rId8" display="https://orcid.org/0009-0001-5290-5544" xr:uid="{A5D22604-2496-BE4F-B9DD-562C5B47E295}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{D172C527-C1C4-C047-A757-BC75CC7426F9}"/>
-    <hyperlink ref="T4" r:id="rId10" xr:uid="{6F8425CF-B855-5A4A-B2B6-34D12B80B2AB}"/>
-    <hyperlink ref="T5" r:id="rId11" xr:uid="{4B38D0AD-2FC7-464D-9060-0D0FBCDDA9CB}"/>
-    <hyperlink ref="T7" r:id="rId12" xr:uid="{C7B4F0EB-6958-F54A-AF58-5BDA16E41654}"/>
-    <hyperlink ref="T9" r:id="rId13" xr:uid="{E2673CF1-94A5-2249-916F-2DCC53FC5CC1}"/>
-    <hyperlink ref="V5" r:id="rId14" xr:uid="{5AE67EF2-5E71-864C-90FE-CC4C98072E15}"/>
-    <hyperlink ref="W5" r:id="rId15" xr:uid="{C859D6CF-4C2E-2746-B2B4-BC6D99CC40FD}"/>
+    <hyperlink ref="Y4" r:id="rId5" xr:uid="{4C866E4E-CAF9-1040-95E4-4C9C2454535B}"/>
+    <hyperlink ref="W4" r:id="rId6" xr:uid="{410C066E-FF05-C942-A96A-A83F5FBDEF4A}"/>
+    <hyperlink ref="U4" r:id="rId7" display="https://orcid.org/0009-0001-5290-5544" xr:uid="{A5D22604-2496-BE4F-B9DD-562C5B47E295}"/>
+    <hyperlink ref="V4" r:id="rId8" xr:uid="{D172C527-C1C4-C047-A757-BC75CC7426F9}"/>
+    <hyperlink ref="T4" r:id="rId9" xr:uid="{6F8425CF-B855-5A4A-B2B6-34D12B80B2AB}"/>
+    <hyperlink ref="T5" r:id="rId10" xr:uid="{4B38D0AD-2FC7-464D-9060-0D0FBCDDA9CB}"/>
+    <hyperlink ref="T7" r:id="rId11" xr:uid="{C7B4F0EB-6958-F54A-AF58-5BDA16E41654}"/>
+    <hyperlink ref="T9" r:id="rId12" xr:uid="{E2673CF1-94A5-2249-916F-2DCC53FC5CC1}"/>
+    <hyperlink ref="V5" r:id="rId13" xr:uid="{5AE67EF2-5E71-864C-90FE-CC4C98072E15}"/>
+    <hyperlink ref="W5" r:id="rId14" xr:uid="{C859D6CF-4C2E-2746-B2B4-BC6D99CC40FD}"/>
+    <hyperlink ref="J4" r:id="rId15" xr:uid="{7D6C4E43-7F6D-5544-AFD2-CD6603480932}"/>
+    <hyperlink ref="I4" r:id="rId16" xr:uid="{F277A869-653E-034D-BD79-6B4A432241DB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
